--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J101-SecteurActivite-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J101-SecteurActivite-RASS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240726120000</t>
+    <t>20241209120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-26T12:00:00+01:00</t>
+    <t>2024-12-09T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -474,7 +474,7 @@
     <t>SA63</t>
   </si>
   <si>
-    <t>Communauté Professionnelle Territoriale de Santé</t>
+    <t>Communauté professionnelle territoriale de santé et équipe de soins spécialisés</t>
   </si>
   <si>
     <t>SA64</t>
